--- a/artfynd/A 7334-2025 artfynd.xlsx
+++ b/artfynd/A 7334-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110259120</v>
+        <v>110259115</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Nordanåker, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578030.5943160817</v>
+        <v>578008</v>
       </c>
       <c r="R2" t="n">
-        <v>7031348.437202711</v>
+        <v>7031388</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,19 +743,9 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110259125</v>
+        <v>110259119</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578010.6243751374</v>
+        <v>578034</v>
       </c>
       <c r="R3" t="n">
-        <v>7031357.364790352</v>
+        <v>7031365</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,19 +840,9 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110259111</v>
+        <v>110259124</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577984.9778669713</v>
+        <v>578008</v>
       </c>
       <c r="R4" t="n">
-        <v>7031415.019252964</v>
+        <v>7031359</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,19 +937,9 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110259119</v>
+        <v>110259125</v>
       </c>
       <c r="B5" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578033.7683143152</v>
+        <v>578011</v>
       </c>
       <c r="R5" t="n">
-        <v>7031365.550345697</v>
+        <v>7031357</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,19 +1034,9 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,12 +1066,7 @@
         <v>110259123</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578007.5384528355</v>
+        <v>578008</v>
       </c>
       <c r="R6" t="n">
-        <v>7031355.04801502</v>
+        <v>7031355</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,19 +1131,9 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,12 +1163,7 @@
         <v>110259122</v>
       </c>
       <c r="B7" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578005.5396616739</v>
+        <v>578006</v>
       </c>
       <c r="R7" t="n">
-        <v>7031437.038803107</v>
+        <v>7031437</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,19 +1232,9 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1360,50 +1266,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110259115</v>
+        <v>110259121</v>
       </c>
       <c r="B8" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Söder om Nordanåker, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578008.5247677419</v>
+        <v>578024</v>
       </c>
       <c r="R8" t="n">
-        <v>7031388.24676133</v>
+        <v>7031353</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,19 +1338,9 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,50 +1367,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110259127</v>
+        <v>110259120</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söder om Nordanåker, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578031.6268123295</v>
+        <v>578031</v>
       </c>
       <c r="R9" t="n">
-        <v>7031453.365253174</v>
+        <v>7031349</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1545,19 +1439,9 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,15 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110259124</v>
+        <v>110259111</v>
       </c>
       <c r="B10" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,21 +1479,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,10 +1503,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578007.8887982876</v>
+        <v>577985</v>
       </c>
       <c r="R10" t="n">
-        <v>7031359.091335098</v>
+        <v>7031415</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1657,19 +1536,9 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,54 +1565,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110259121</v>
+        <v>110259127</v>
       </c>
       <c r="B11" t="n">
-        <v>56806</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Söder om Nordanåker, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578023.7444079213</v>
+        <v>578031</v>
       </c>
       <c r="R11" t="n">
-        <v>7031353.201580917</v>
+        <v>7031453</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1773,19 +1633,9 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 7334-2025 artfynd.xlsx
+++ b/artfynd/A 7334-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259115</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259119</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259124</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259125</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259123</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259122</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259121</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259120</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259111</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1659,8 +1709,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259127</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>